--- a/fhir/StructureDefinition-ehealth-auditevent.xlsx
+++ b/fhir/StructureDefinition-ehealth-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,7 +367,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -490,7 +490,7 @@
     <t>Type of event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-event-type</t>
+    <t>http://hl7.org/fhir/ValueSet/audit-event-type|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -523,7 +523,7 @@
     <t>Sub-type of event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-event-sub-type</t>
+    <t>http://hl7.org/fhir/ValueSet/audit-event-sub-type|4.0.1</t>
   </si>
   <si>
     <t>EventTypeCode</t>
@@ -794,7 +794,7 @@
     <t>The Participation type of the agent to the event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participation-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/participation-role-type|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -833,7 +833,7 @@
     <t>What security role enabled the agent to participate in the event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>.role</t>
@@ -849,7 +849,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PractitionerRole|Practitioner|Organization|Device|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(PractitionerRole|4.0.1|Practitioner|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>AuditEvent.agent.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1011,7 +1011,7 @@
     <t>Used when the event is about exporting/importing onto media.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/dicm-405-mediatype</t>
+    <t>http://hl7.org/fhir/ValueSet/dicm-405-mediatype|4.0.1</t>
   </si>
   <si>
     <t>.player.description.mediaType</t>
@@ -1191,7 +1191,7 @@
     <t>Code specifying the type of system that detected and recorded the event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-source-type</t>
+    <t>http://hl7.org/fhir/ValueSet/audit-source-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -1247,7 +1247,7 @@
     <t>AuditEvent.entity.what</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1281,7 +1281,7 @@
     <t>Code for the entity type involved in the audit event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-entity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/audit-entity-type|4.0.1</t>
   </si>
   <si>
     <t>[self::Act].code or role.player.code</t>
@@ -1311,7 +1311,7 @@
     <t>Code representing the role the entity played in the audit event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/object-role</t>
+    <t>http://hl7.org/fhir/ValueSet/object-role|4.0.1</t>
   </si>
   <si>
     <t>role.code (not sure what this would mean for an Act)</t>
@@ -1341,7 +1341,7 @@
     <t>Institutional policies for privacy and security may optionally fall under different accountability rules based on data life cycle. This provides a differentiating value for those cases.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/object-lifecycle-events</t>
+    <t>http://hl7.org/fhir/ValueSet/object-lifecycle-events|4.0.1</t>
   </si>
   <si>
     <t>target of ObservationEvent[code="lifecycle"].value</t>
@@ -1817,7 +1817,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.81640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1832,7 +1832,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="65.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.53515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.74609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-auditevent.xlsx
+++ b/fhir/StructureDefinition-ehealth-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-auditevent.xlsx
+++ b/fhir/StructureDefinition-ehealth-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-auditevent.xlsx
+++ b/fhir/StructureDefinition-ehealth-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-auditevent.xlsx
+++ b/fhir/StructureDefinition-ehealth-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-auditevent.xlsx
+++ b/fhir/StructureDefinition-ehealth-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-auditevent.xlsx
+++ b/fhir/StructureDefinition-ehealth-auditevent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
